--- a/data/source/xlsx/Agents.xlsx
+++ b/data/source/xlsx/Agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,28 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>Codificatore del dataset GaddAtlas (dottorato in Digital Humanities, Università di Bologna, FICLIT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Emilio Manzotti</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>scholar</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Commento al cap. VIII del Pasticciaccio (Manzotti 2010, «Per leggere» 19)</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Agents.xlsx
+++ b/data/source/xlsx/Agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,72 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>Commento al cap. VIII del Pasticciaccio (Manzotti 2010, «Per leggere» 19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>perosa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Giulia Perosa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>scholar</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Gadda e il paesaggio (Perosa 2023a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lugnani</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Lucio Lugnani</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>scholar</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Citato in Perosa 2023a, p. 104, n. 97</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cortellessa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Andrea Cortellessa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>scholar</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Archeologia con pescecane (Cortellessa 2023)</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Agents.xlsx
+++ b/data/source/xlsx/Agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,50 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pinotti</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Giorgio Pinotti</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>scholar</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Curatore di QP (Adelphi 2018) e di RR II; Pinotti 2016, 2024, 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>L. Matt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>scholar</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Matt e Pinotti 2022 (appunti autografi per la revisione del romanesco)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/Agents.xlsx
+++ b/data/source/xlsx/Agents.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Curatore di QP (Adelphi 2018) e di RR II; Pinotti 2016, 2024, 2025</t>
+          <t>Curatore di QPa (QP, Adelphi 2018) e di RR II; Pinotti 2016, 2024, 2025</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Agents.xlsx
+++ b/data/source/xlsx/Agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,6 +592,116 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Maria Antonietta Terzoli</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>scholar</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Commento a «Quer pasticciaccio brutto de via Merulana» (Terzoli 2015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>italia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Paola Italia</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>scholar</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Editing Duemila (Italia 2020)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>grassadonia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fabio Grassadonia</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>scholar</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Grassadonia, Lagossi e Marchetti 1997a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>lagossi</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Paola Lagossi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>scholar</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Grassadonia, Lagossi e Marchetti 1997a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>marchetti</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mario Marchetti</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>scholar</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Grassadonia, Lagossi e Marchetti 1997a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
